--- a/ci-cd-merge-resolver/repoCollector/datasets/struts.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/struts.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,55 +44,76 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>f36c7678c5cdd04614a9c3a0090d15350714f4af</t>
-  </si>
-  <si>
-    <t>c4d3ef8687a30f715ca9494e130d1776c7d2427d</t>
-  </si>
-  <si>
-    <t>76bbe60a78b2b47fcb961f85d3db9971d85fc2d1</t>
-  </si>
-  <si>
-    <t>b72200aabf3c687bb3690a89035f5baa29636631</t>
-  </si>
-  <si>
-    <t>16e7c9b459276293c692da49d09ec2a4c2fa42b9</t>
-  </si>
-  <si>
-    <t>bea1c6f09f05ab88cca2d7cc14b2d4a6fb999a9a</t>
-  </si>
-  <si>
-    <t>4c370110204cc4fcc42d30d7537d2c5cc1486e3b</t>
-  </si>
-  <si>
-    <t>fbb31ee65b972f2c64fba470f9e88d51aa169a70</t>
-  </si>
-  <si>
-    <t>c0940529690697611aaab38ea9ea1186d909267b</t>
-  </si>
-  <si>
-    <t>e1167d42beefa26686b31e797179f0c396930ac8</t>
-  </si>
-  <si>
-    <t>b2bfdc5c88a13e82d647e7ae836089a12ce001fe</t>
-  </si>
-  <si>
-    <t>69a7195df7ed673f9fa641920e97ade462d9b6e7</t>
-  </si>
-  <si>
-    <t>f3c160d9d60a3ef04c15b0333ad14e3c978fcca2</t>
-  </si>
-  <si>
-    <t>ed06d61f2fcfad32aeba28ae6e2f5e7335f251dc</t>
-  </si>
-  <si>
-    <t>0566a207f4f6efb5e3a36d63b30d9fa5abe994b9</t>
-  </si>
-  <si>
-    <t>d7df9ce9981558d230c40cd065d2c67aa110b657</t>
-  </si>
-  <si>
-    <t>7929d8634c58b60709db1133e8a6d42a30c2827f</t>
+    <t>70fdc00f664947732840e16f4de06ea0cf10487a</t>
+  </si>
+  <si>
+    <t>9ad0dfba1d74f494e33b1ba5fab1ce8c7d3f6412</t>
+  </si>
+  <si>
+    <t>cdbf697ad82a5682956fb0bfbe10528c26bbbaf4</t>
+  </si>
+  <si>
+    <t>2fada1ec05e61dfb0b3e43ab447a7673d689c684</t>
+  </si>
+  <si>
+    <t>0d4905038119f614f021af5738154079b30bca24</t>
+  </si>
+  <si>
+    <t>fab687a07e8d873c82465b29188100debf61097f</t>
+  </si>
+  <si>
+    <t>bab451c6d80ee9b2685570d797e505768ff8bbe4</t>
+  </si>
+  <si>
+    <t>abd8c6bfb5fc3a9e3f9f3767bb10acd9b7c4836d</t>
+  </si>
+  <si>
+    <t>8b6078570ebec52bfd23f3667d9736fc30bbc8d3</t>
+  </si>
+  <si>
+    <t>3163d6c38b4a6f4f7d6e5447476934beebb398fe</t>
+  </si>
+  <si>
+    <t>b48082a8115dee04f33c6db29aacee64973424c6</t>
+  </si>
+  <si>
+    <t>104bd92b88361978d3b8014db44e8a9a9b63077f</t>
+  </si>
+  <si>
+    <t>d1fbf6a8972908fac3a41ec0e2756fe4eec1afb6</t>
+  </si>
+  <si>
+    <t>6c19875c786c03a33658f633d5c6a3425bbd5aaf</t>
+  </si>
+  <si>
+    <t>8852e3d1183f1ce18dbf8dc9bb1da465eaa9f1c3</t>
+  </si>
+  <si>
+    <t>ae5605ff8872daa08f12c84fb7a2b30f5f57e8ea</t>
+  </si>
+  <si>
+    <t>4de8309d0aebb75d409119f2d4a6d06491dda2b4</t>
+  </si>
+  <si>
+    <t>6d623ebb56a6fb801753b2c64614c6188e9c149d</t>
+  </si>
+  <si>
+    <t>32597350fe8839721791b3d29b7a5993bb6af1aa</t>
+  </si>
+  <si>
+    <t>b198e3bf3d70f7bfd5b8d560a848261b4855be2e</t>
+  </si>
+  <si>
+    <t>f9b7ebb87eb2beeffb2ca1b0f3b421b0cef4d658</t>
+  </si>
+  <si>
+    <t>dc645bec4d6aa21b88372a06f0eca0c7b7b0d38b</t>
+  </si>
+  <si>
+    <t>aee171c3b8ad401006612c4df44ed540fb2ed7e3</t>
+  </si>
+  <si>
+    <t>eddab32e7526ad2ad56a247988ab7e2655bccc9f</t>
   </si>
 </sst>
 </file>
@@ -137,7 +158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -183,7 +204,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2323.0</v>
+        <v>4539.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -198,10 +219,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>83.13400268554688</v>
+        <v>9.03499984741211</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -215,7 +236,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2391.0</v>
+        <v>4513.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -230,10 +251,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>84.8539810180664</v>
+        <v>8.54699993133545</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -241,16 +262,16 @@
         <v>16</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2366.0</v>
+        <v>4513.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>1.0</v>
@@ -262,30 +283,30 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>77.15499877929688</v>
+        <v>8.380999565124512</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>20</v>
-      </c>
       <c r="D5" t="n" s="0">
-        <v>2339.0</v>
+        <v>4496.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -294,30 +315,30 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>76.0570297241211</v>
+        <v>8.246000289916992</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>23</v>
-      </c>
       <c r="D6" t="n" s="0">
-        <v>2545.0</v>
+        <v>4531.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -326,42 +347,138 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>93.29598999023438</v>
+        <v>8.723999977111816</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="D7" t="n" s="0">
+        <v>1693.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>20.961999893188477</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="B8" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="D7" t="n" s="0">
-        <v>2517.0</v>
-      </c>
-      <c r="E7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G7" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n" s="0">
-        <v>83.74401092529297</v>
-      </c>
-      <c r="J7" t="b" s="0">
-        <v>1</v>
+      <c r="C8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>1679.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>20.999000549316406</v>
+      </c>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>4490.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>5.1539998054504395</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>1761.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>35.808998107910156</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
